--- a/Избыток_и_недостаток_обучения.xlsx
+++ b/Избыток_и_недостаток_обучения.xlsx
@@ -15,9 +15,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Избыток'!$A$1:$G$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Избыток'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Избыток'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Недостаток'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Недостаток'!$A$1:$G$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Недостаток'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Недостаток'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Недостаток'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Расшифровка программы 46а'!$A$1:$I$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Расшифровка программы 46а'!$1:$1</definedName>
   </definedNames>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +57,14 @@
       <color rgb="FF9A3412"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF991B1B"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFECACA"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,6 +134,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -595,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -644,8 +664,41 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="64" customHeight="1">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Недостаток обучения руководителей структурных подразделений и их заместителей по программе 46а</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>46а — общие вопросы охраны труда и функционирования системы управления охраной труда</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Руководители структурных подразделений и их заместители</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>ПП РФ от 24.12.2021 № 2464, п. 46 подп. «а», п. 53 подп. «б»</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>В сводной нет плюса по программе 46а: заместитель начальника участка, заведующий складом АХОВ, начальник участка, руководитель строительства группы объектов, начальник смены, заместитель начальника пылевентиляционной службы.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>

--- a/Избыток_и_недостаток_обучения.xlsx
+++ b/Избыток_и_недостаток_обучения.xlsx
@@ -15,9 +15,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Избыток'!$A$1:$G$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Избыток'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Избыток'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Недостаток'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Недостаток'!$A$1:$G$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Недостаток'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Недостаток'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Недостаток'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Расшифровка программы 46а'!$A$1:$I$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Расшифровка программы 46а'!$1:$1</definedName>
   </definedNames>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -697,8 +697,41 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Недостаток обучения по программе 46б</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>46б — безопасные методы и приемы выполнения работ при вредных и опасных факторах</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Работники рабочих профессий; работники с обучением по 46в или СИЗ</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>ПП РФ от 24.12.2021 № 2464, п. 46 подп. «б», п. 53 подп. «д»</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Нет плюса по 46б. Из них 10 работников рабочих профессий. Ещё 6 отмечены, потому что есть обучение по 46в или по СИЗ, а программы 46б нет: два руководителя участка, делопроизводитель, ведущий инженер ППР и два геолога.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
